--- a/reports/一级子公司B_利润表_2025-12.xlsx
+++ b/reports/一级子公司B_利润表_2025-12.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>46685657</v>
+        <v>61680475</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>13830914</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>171795115</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>193406</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>2422051</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>173743</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>2179191</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>144643</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>1815271</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>135007</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>1693536</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>77231</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>967372</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>58035</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>725338</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>46685657</v>
+        <v>60898410</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>13048849</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>7792595</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>96732966</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1170505</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>14515217</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>585488</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>7260665</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>3900729</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>48424031</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>389456</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>4843940</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>291437</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>3633588</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>484509</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>6055981</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>386700</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>4843944</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>46605888</v>
+        <v>46322701</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>580825625</v>
+        <v>581089259</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>79769</v>
+        <v>79524</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>959963</v>
+        <v>960085</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>867980</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>10886429</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>579356</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>7254983</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>42911684</v>
+        <v>55440471</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>24312757</v>
+        <v>31358208</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>146210</v>
+        <v>7000669</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1814958</v>
+        <v>87040689</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>24166547</v>
+        <v>24357539</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>302510325</v>
+        <v>302303384</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1463297</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>18145004</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>468378</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5808859</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>292507</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3631978</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>350416</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4359688</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>262207</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3270262</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>174365</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2180123</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>144973</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1816417</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1170054</v>
+        <v>1157870</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>14519723</v>
+        <v>14526502</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>38648</v>
+        <v>38568</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>484015</v>
+        <v>484018</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2430299</v>
+        <v>2411310</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>30248795</v>
+        <v>30238473</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>14546959</v>
+        <v>14487221</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>181507984</v>
+        <v>181367219</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2419604</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>30221159</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>451615</v>
+        <v>450115</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>5400202</v>
+        <v>5393899</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>398008</v>
+        <v>401077</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4799869</v>
+        <v>4795272</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>30174</v>
+        <v>30140</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>360005</v>
+        <v>359761</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>135783</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1619625</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>256133</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3176897</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>90450</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1080732</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>67716</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>810801</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>112594</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1351527</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>363142</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4541849</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>59767</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>720594</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>44756</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>540231</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>74550</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>899964</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>52210</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>629684</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>37347</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>449606</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>29943</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>359608</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>22513</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>269696</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3773973</v>
+        <v>6361990</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-105089</v>
+        <v>4380329</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>146355</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1814703</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>37720</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>450139</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>60324</v>
+        <v>60288</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>720017</v>
+        <v>720523</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>3713649</v>
+        <v>6448057</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1810534</v>
+        <v>1800908</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>21599867</v>
+        <v>21624511</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>1903115</v>
+        <v>4647149</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>1903115</v>
+        <v>4647149</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>1903115</v>
+        <v>4647149</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>1903115</v>
+        <v>4647149</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1903115</v>
+        <v>4647149</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
